--- a/Data/IceStation1c/09aug2025coring/20250809-PS149_32-1-SI_corer_9cm-019-FYI-RHO.xlsx
+++ b/Data/IceStation1c/09aug2025coring/20250809-PS149_32-1-SI_corer_9cm-019-FYI-RHO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evsalg001\Documents\MATLAB\Contrasts coring\Data\IceStation1c\09aug2025coring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA60233-3C67-4FA0-B0A2-BF7FE430E46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB0C285-6422-4F47-9A78-40CF3587F1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="19410" windowHeight="20880" tabRatio="726" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="615" windowWidth="19410" windowHeight="20985" tabRatio="726" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata-core" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="CT" sheetId="12" r:id="rId12"/>
     <sheet name="lists" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1097,10 +1097,10 @@
     <t>smaller bubbles</t>
   </si>
   <si>
-    <t>rho_parafine=0.835</t>
+    <t>Tlab=-22</t>
   </si>
   <si>
-    <t>Tlab=-22</t>
+    <t>rho_parafine=0.834</t>
   </si>
 </sst>
 </file>
@@ -1696,6 +1696,18 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1705,19 +1717,10 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1726,7 +1729,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1735,20 +1738,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -23747,14 +23747,14 @@
       <c r="G1" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="156" t="s">
+      <c r="H1" s="157" t="s">
         <v>92</v>
       </c>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156" t="s">
+      <c r="I1" s="157"/>
+      <c r="J1" s="157" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="156"/>
+      <c r="K1" s="157"/>
       <c r="L1" s="60"/>
       <c r="M1" s="58" t="s">
         <v>95</v>
@@ -23765,10 +23765,10 @@
       </c>
       <c r="P1" s="19"/>
       <c r="Q1" s="9"/>
-      <c r="R1" s="159" t="s">
+      <c r="R1" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="S1" s="159"/>
+      <c r="S1" s="161"/>
       <c r="T1" s="9"/>
       <c r="U1" s="58" t="s">
         <v>85</v>
@@ -28123,11 +28123,11 @@
         <v>20</v>
       </c>
       <c r="B3" s="24"/>
-      <c r="C3" s="145" t="s">
+      <c r="C3" s="149" t="s">
         <v>297</v>
       </c>
-      <c r="D3" s="145"/>
-      <c r="E3" s="145"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -28154,11 +28154,11 @@
         <v>21</v>
       </c>
       <c r="B4" s="26"/>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="150" t="s">
         <v>306</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -28212,11 +28212,11 @@
     <row r="6" spans="1:25" ht="13.5" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="147" t="s">
+      <c r="C6" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="147"/>
-      <c r="E6" s="147"/>
+      <c r="D6" s="151"/>
+      <c r="E6" s="151"/>
       <c r="F6" s="144" t="s">
         <v>24</v>
       </c>
@@ -29136,11 +29136,11 @@
         <v>67</v>
       </c>
       <c r="B33" s="53"/>
-      <c r="C33" s="149"/>
-      <c r="D33" s="149"/>
-      <c r="E33" s="149"/>
-      <c r="F33" s="149"/>
-      <c r="G33" s="149"/>
+      <c r="C33" s="145"/>
+      <c r="D33" s="145"/>
+      <c r="E33" s="145"/>
+      <c r="F33" s="145"/>
+      <c r="G33" s="145"/>
       <c r="H33" s="22"/>
       <c r="I33" s="22"/>
       <c r="J33" s="22"/>
@@ -29382,11 +29382,11 @@
       <c r="Y40" s="22"/>
     </row>
     <row r="41" spans="1:25">
-      <c r="A41" s="150" t="s">
+      <c r="A41" s="146" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="150"/>
-      <c r="C41" s="150"/>
+      <c r="B41" s="146"/>
+      <c r="C41" s="146"/>
       <c r="D41" s="22"/>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
@@ -29411,14 +29411,14 @@
       <c r="Y41" s="22"/>
     </row>
     <row r="42" spans="1:25" ht="63.75" customHeight="1">
-      <c r="A42" s="151" t="s">
+      <c r="A42" s="147" t="s">
         <v>320</v>
       </c>
-      <c r="B42" s="151"/>
-      <c r="C42" s="151"/>
-      <c r="D42" s="151"/>
-      <c r="E42" s="151"/>
-      <c r="F42" s="151"/>
+      <c r="B42" s="147"/>
+      <c r="C42" s="147"/>
+      <c r="D42" s="147"/>
+      <c r="E42" s="147"/>
+      <c r="F42" s="147"/>
       <c r="G42" s="22"/>
       <c r="H42" s="22"/>
       <c r="I42" s="22"/>
@@ -29711,21 +29711,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="C33:G33"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A42:F42"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="C6:E6"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="date" prompt="Date in international format: YYYY-MM-DD" sqref="C12:D12" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -30968,11 +30968,11 @@
       <c r="B2" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="153" t="s">
+      <c r="C2" s="154" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
       <c r="F2" s="68"/>
       <c r="G2" s="68"/>
       <c r="H2" s="68"/>
@@ -31002,11 +31002,11 @@
       <c r="B3" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="154" t="s">
+      <c r="C3" s="155" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="154"/>
-      <c r="E3" s="154"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="155"/>
       <c r="F3" s="68"/>
       <c r="G3" s="68"/>
       <c r="H3" s="68"/>
@@ -31032,9 +31032,9 @@
     <row r="4" spans="1:26" ht="15.75">
       <c r="A4" s="70"/>
       <c r="B4" s="70"/>
-      <c r="C4" s="155"/>
-      <c r="D4" s="155"/>
-      <c r="E4" s="155"/>
+      <c r="C4" s="153"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="153"/>
       <c r="F4" s="22"/>
       <c r="G4" s="22"/>
       <c r="H4" s="22"/>
@@ -31060,9 +31060,9 @@
     <row r="5" spans="1:26" ht="15.75">
       <c r="A5" s="70"/>
       <c r="B5" s="70"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
@@ -31088,9 +31088,9 @@
     <row r="6" spans="1:26" ht="15.75">
       <c r="A6" s="70"/>
       <c r="B6" s="70"/>
-      <c r="C6" s="155"/>
-      <c r="D6" s="155"/>
-      <c r="E6" s="155"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
       <c r="F6" s="22"/>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
@@ -31116,9 +31116,9 @@
     <row r="7" spans="1:26" ht="15.75">
       <c r="A7" s="70"/>
       <c r="B7" s="70"/>
-      <c r="C7" s="155"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="155"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
@@ -31144,9 +31144,9 @@
     <row r="8" spans="1:26" ht="15.75">
       <c r="A8" s="70"/>
       <c r="B8" s="70"/>
-      <c r="C8" s="155"/>
-      <c r="D8" s="155"/>
-      <c r="E8" s="155"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="153"/>
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
       <c r="H8" s="22"/>
@@ -31172,9 +31172,9 @@
     <row r="9" spans="1:26" ht="15.75">
       <c r="A9" s="70"/>
       <c r="B9" s="70"/>
-      <c r="C9" s="155"/>
-      <c r="D9" s="155"/>
-      <c r="E9" s="155"/>
+      <c r="C9" s="153"/>
+      <c r="D9" s="153"/>
+      <c r="E9" s="153"/>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
@@ -31200,9 +31200,9 @@
     <row r="10" spans="1:26" ht="15.75">
       <c r="A10" s="70"/>
       <c r="B10" s="70"/>
-      <c r="C10" s="155"/>
-      <c r="D10" s="155"/>
-      <c r="E10" s="155"/>
+      <c r="C10" s="153"/>
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
       <c r="H10" s="22"/>
@@ -31228,9 +31228,9 @@
     <row r="11" spans="1:26" ht="15.75">
       <c r="A11" s="70"/>
       <c r="B11" s="70"/>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
+      <c r="C11" s="153"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="153"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
@@ -31256,9 +31256,9 @@
     <row r="12" spans="1:26" ht="15.75">
       <c r="A12" s="70"/>
       <c r="B12" s="70"/>
-      <c r="C12" s="155"/>
-      <c r="D12" s="155"/>
-      <c r="E12" s="155"/>
+      <c r="C12" s="153"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="153"/>
       <c r="F12" s="22"/>
       <c r="G12" s="22"/>
       <c r="H12" s="22"/>
@@ -31284,9 +31284,9 @@
     <row r="13" spans="1:26" ht="15.75">
       <c r="A13" s="70"/>
       <c r="B13" s="70"/>
-      <c r="C13" s="155"/>
-      <c r="D13" s="155"/>
-      <c r="E13" s="155"/>
+      <c r="C13" s="153"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
       <c r="F13" s="22"/>
       <c r="G13" s="22"/>
       <c r="H13" s="22"/>
@@ -31312,9 +31312,9 @@
     <row r="14" spans="1:26" ht="15.75">
       <c r="A14" s="70"/>
       <c r="B14" s="70"/>
-      <c r="C14" s="155"/>
-      <c r="D14" s="155"/>
-      <c r="E14" s="155"/>
+      <c r="C14" s="153"/>
+      <c r="D14" s="153"/>
+      <c r="E14" s="153"/>
       <c r="F14" s="22"/>
       <c r="G14" s="22"/>
       <c r="H14" s="22"/>
@@ -31338,9 +31338,9 @@
       <c r="Z14" s="22"/>
     </row>
     <row r="15" spans="1:26">
-      <c r="C15" s="155"/>
-      <c r="D15" s="155"/>
-      <c r="E15" s="155"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153"/>
+      <c r="E15" s="153"/>
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
       <c r="H15" s="22"/>
@@ -31366,9 +31366,9 @@
     <row r="16" spans="1:26" ht="15.75">
       <c r="A16" s="70"/>
       <c r="B16" s="70"/>
-      <c r="C16" s="155"/>
-      <c r="D16" s="155"/>
-      <c r="E16" s="155"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
@@ -31394,9 +31394,9 @@
     <row r="17" spans="1:26" ht="15.75">
       <c r="A17" s="70"/>
       <c r="B17" s="70"/>
-      <c r="C17" s="155"/>
-      <c r="D17" s="155"/>
-      <c r="E17" s="155"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="22"/>
@@ -31422,9 +31422,9 @@
     <row r="18" spans="1:26" ht="15.75">
       <c r="A18" s="70"/>
       <c r="B18" s="70"/>
-      <c r="C18" s="155"/>
-      <c r="D18" s="155"/>
-      <c r="E18" s="155"/>
+      <c r="C18" s="153"/>
+      <c r="D18" s="153"/>
+      <c r="E18" s="153"/>
       <c r="F18" s="22"/>
       <c r="G18" s="22"/>
       <c r="H18" s="22"/>
@@ -31450,9 +31450,9 @@
     <row r="19" spans="1:26" ht="15.75">
       <c r="A19" s="70"/>
       <c r="B19" s="70"/>
-      <c r="C19" s="155"/>
-      <c r="D19" s="155"/>
-      <c r="E19" s="155"/>
+      <c r="C19" s="153"/>
+      <c r="D19" s="153"/>
+      <c r="E19" s="153"/>
       <c r="F19" s="22"/>
       <c r="G19" s="22"/>
       <c r="H19" s="22"/>
@@ -31478,9 +31478,9 @@
     <row r="20" spans="1:26" ht="15.75">
       <c r="A20" s="70"/>
       <c r="B20" s="70"/>
-      <c r="C20" s="155"/>
-      <c r="D20" s="155"/>
-      <c r="E20" s="155"/>
+      <c r="C20" s="153"/>
+      <c r="D20" s="153"/>
+      <c r="E20" s="153"/>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
       <c r="H20" s="22"/>
@@ -31506,9 +31506,9 @@
     <row r="21" spans="1:26" ht="15.75">
       <c r="A21" s="70"/>
       <c r="B21" s="70"/>
-      <c r="C21" s="155"/>
-      <c r="D21" s="155"/>
-      <c r="E21" s="155"/>
+      <c r="C21" s="153"/>
+      <c r="D21" s="153"/>
+      <c r="E21" s="153"/>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
       <c r="H21" s="22"/>
@@ -31534,9 +31534,9 @@
     <row r="22" spans="1:26" ht="15.75">
       <c r="A22" s="70"/>
       <c r="B22" s="70"/>
-      <c r="C22" s="155"/>
-      <c r="D22" s="155"/>
-      <c r="E22" s="155"/>
+      <c r="C22" s="153"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="153"/>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
       <c r="H22" s="22"/>
@@ -31562,9 +31562,9 @@
     <row r="23" spans="1:26" ht="15.75">
       <c r="A23" s="70"/>
       <c r="B23" s="70"/>
-      <c r="C23" s="155"/>
-      <c r="D23" s="155"/>
-      <c r="E23" s="155"/>
+      <c r="C23" s="153"/>
+      <c r="D23" s="153"/>
+      <c r="E23" s="153"/>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
@@ -31590,9 +31590,9 @@
     <row r="24" spans="1:26" ht="15.75">
       <c r="A24" s="70"/>
       <c r="B24" s="70"/>
-      <c r="C24" s="155"/>
-      <c r="D24" s="155"/>
-      <c r="E24" s="155"/>
+      <c r="C24" s="153"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="153"/>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
@@ -31618,9 +31618,9 @@
     <row r="25" spans="1:26" ht="15.75">
       <c r="A25" s="70"/>
       <c r="B25" s="70"/>
-      <c r="C25" s="155"/>
-      <c r="D25" s="155"/>
-      <c r="E25" s="155"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
@@ -31646,9 +31646,9 @@
     <row r="26" spans="1:26" ht="15.75">
       <c r="A26" s="70"/>
       <c r="B26" s="70"/>
-      <c r="C26" s="155"/>
-      <c r="D26" s="155"/>
-      <c r="E26" s="155"/>
+      <c r="C26" s="153"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="153"/>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
       <c r="H26" s="22"/>
@@ -31674,9 +31674,9 @@
     <row r="27" spans="1:26" ht="15.75">
       <c r="A27" s="70"/>
       <c r="B27" s="70"/>
-      <c r="C27" s="155"/>
-      <c r="D27" s="155"/>
-      <c r="E27" s="155"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
@@ -31702,9 +31702,9 @@
     <row r="28" spans="1:26" ht="15.75">
       <c r="A28" s="70"/>
       <c r="B28" s="70"/>
-      <c r="C28" s="155"/>
-      <c r="D28" s="155"/>
-      <c r="E28" s="155"/>
+      <c r="C28" s="153"/>
+      <c r="D28" s="153"/>
+      <c r="E28" s="153"/>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
@@ -31730,9 +31730,9 @@
     <row r="29" spans="1:26" ht="15.75">
       <c r="A29" s="70"/>
       <c r="B29" s="70"/>
-      <c r="C29" s="155"/>
-      <c r="D29" s="155"/>
-      <c r="E29" s="155"/>
+      <c r="C29" s="153"/>
+      <c r="D29" s="153"/>
+      <c r="E29" s="153"/>
       <c r="F29" s="22"/>
       <c r="G29" s="22"/>
       <c r="H29" s="22"/>
@@ -31758,9 +31758,9 @@
     <row r="30" spans="1:26" ht="15.75">
       <c r="A30" s="70"/>
       <c r="B30" s="70"/>
-      <c r="C30" s="155"/>
-      <c r="D30" s="155"/>
-      <c r="E30" s="155"/>
+      <c r="C30" s="153"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
       <c r="F30" s="22"/>
       <c r="G30" s="22"/>
       <c r="H30" s="22"/>
@@ -31786,9 +31786,9 @@
     <row r="31" spans="1:26" ht="15.75">
       <c r="A31" s="70"/>
       <c r="B31" s="70"/>
-      <c r="C31" s="155"/>
-      <c r="D31" s="155"/>
-      <c r="E31" s="155"/>
+      <c r="C31" s="153"/>
+      <c r="D31" s="153"/>
+      <c r="E31" s="153"/>
       <c r="F31" s="22"/>
       <c r="G31" s="22"/>
       <c r="H31" s="22"/>
@@ -31814,9 +31814,9 @@
     <row r="32" spans="1:26" ht="15.75">
       <c r="A32" s="70"/>
       <c r="B32" s="70"/>
-      <c r="C32" s="155"/>
-      <c r="D32" s="155"/>
-      <c r="E32" s="155"/>
+      <c r="C32" s="153"/>
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
       <c r="F32" s="22"/>
       <c r="G32" s="22"/>
       <c r="H32" s="22"/>
@@ -31842,9 +31842,9 @@
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="70"/>
       <c r="B33" s="70"/>
-      <c r="C33" s="155"/>
-      <c r="D33" s="155"/>
-      <c r="E33" s="155"/>
+      <c r="C33" s="153"/>
+      <c r="D33" s="153"/>
+      <c r="E33" s="153"/>
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
@@ -31870,9 +31870,9 @@
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="70"/>
       <c r="B34" s="70"/>
-      <c r="C34" s="155"/>
-      <c r="D34" s="155"/>
-      <c r="E34" s="155"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="153"/>
+      <c r="E34" s="153"/>
       <c r="F34" s="22"/>
       <c r="G34" s="22"/>
       <c r="H34" s="22"/>
@@ -31898,9 +31898,9 @@
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="70"/>
       <c r="B35" s="70"/>
-      <c r="C35" s="155"/>
-      <c r="D35" s="155"/>
-      <c r="E35" s="155"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="153"/>
+      <c r="E35" s="153"/>
       <c r="F35" s="22"/>
       <c r="G35" s="22"/>
       <c r="H35" s="22"/>
@@ -31926,9 +31926,9 @@
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="70"/>
       <c r="B36" s="70"/>
-      <c r="C36" s="155"/>
-      <c r="D36" s="155"/>
-      <c r="E36" s="155"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="153"/>
+      <c r="E36" s="153"/>
       <c r="F36" s="22"/>
       <c r="G36" s="22"/>
       <c r="H36" s="22"/>
@@ -31954,9 +31954,9 @@
     <row r="37" spans="1:26" ht="15.75">
       <c r="A37" s="70"/>
       <c r="B37" s="70"/>
-      <c r="C37" s="155"/>
-      <c r="D37" s="155"/>
-      <c r="E37" s="155"/>
+      <c r="C37" s="153"/>
+      <c r="D37" s="153"/>
+      <c r="E37" s="153"/>
       <c r="F37" s="22"/>
       <c r="G37" s="22"/>
       <c r="H37" s="22"/>
@@ -31982,9 +31982,9 @@
     <row r="38" spans="1:26" ht="15.75">
       <c r="A38" s="70"/>
       <c r="B38" s="70"/>
-      <c r="C38" s="155"/>
-      <c r="D38" s="155"/>
-      <c r="E38" s="155"/>
+      <c r="C38" s="153"/>
+      <c r="D38" s="153"/>
+      <c r="E38" s="153"/>
       <c r="F38" s="22"/>
       <c r="G38" s="22"/>
       <c r="H38" s="22"/>
@@ -32010,9 +32010,9 @@
     <row r="39" spans="1:26" ht="15.75">
       <c r="A39" s="70"/>
       <c r="B39" s="70"/>
-      <c r="C39" s="155"/>
-      <c r="D39" s="155"/>
-      <c r="E39" s="155"/>
+      <c r="C39" s="153"/>
+      <c r="D39" s="153"/>
+      <c r="E39" s="153"/>
       <c r="F39" s="22"/>
       <c r="G39" s="22"/>
       <c r="H39" s="22"/>
@@ -32065,6 +32065,36 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="C39:E39"/>
@@ -32073,36 +32103,6 @@
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -32184,10 +32184,10 @@
       <c r="C2" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="156" t="s">
+      <c r="D2" s="157" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="156"/>
+      <c r="E2" s="157"/>
       <c r="F2" s="1" t="s">
         <v>95</v>
       </c>
@@ -32222,10 +32222,10 @@
       <c r="C3" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="157" t="s">
+      <c r="D3" s="158" t="s">
         <v>106</v>
       </c>
-      <c r="E3" s="157"/>
+      <c r="E3" s="158"/>
       <c r="F3" s="72" t="s">
         <v>1</v>
       </c>
@@ -32257,8 +32257,8 @@
       <c r="B4" s="62">
         <v>0.72</v>
       </c>
-      <c r="D4" s="158"/>
-      <c r="E4" s="158"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
       <c r="F4" s="6" t="s">
         <v>321</v>
       </c>
@@ -32287,10 +32287,10 @@
       <c r="B5" s="6">
         <v>0.12</v>
       </c>
-      <c r="D5" s="158" t="s">
+      <c r="D5" s="156" t="s">
         <v>181</v>
       </c>
-      <c r="E5" s="158"/>
+      <c r="E5" s="156"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -32313,8 +32313,8 @@
       <c r="Z5" s="9"/>
     </row>
     <row r="6" spans="1:26">
-      <c r="D6" s="158"/>
-      <c r="E6" s="158"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
@@ -32338,8 +32338,8 @@
     </row>
     <row r="7" spans="1:26">
       <c r="C7"/>
-      <c r="D7" s="158"/>
-      <c r="E7" s="158"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
@@ -32363,8 +32363,8 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="62"/>
-      <c r="D8" s="158"/>
-      <c r="E8" s="158"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -32388,8 +32388,8 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="62"/>
-      <c r="D9" s="158"/>
-      <c r="E9" s="158"/>
+      <c r="D9" s="156"/>
+      <c r="E9" s="156"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
@@ -32413,8 +32413,8 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="62"/>
-      <c r="D10" s="158"/>
-      <c r="E10" s="158"/>
+      <c r="D10" s="156"/>
+      <c r="E10" s="156"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
@@ -32438,8 +32438,8 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="62"/>
-      <c r="D11" s="158"/>
-      <c r="E11" s="158"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="156"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
@@ -32463,8 +32463,8 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="62"/>
-      <c r="D12" s="158"/>
-      <c r="E12" s="158"/>
+      <c r="D12" s="156"/>
+      <c r="E12" s="156"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
@@ -32488,8 +32488,8 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="62"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="158"/>
+      <c r="D13" s="156"/>
+      <c r="E13" s="156"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
@@ -32513,8 +32513,8 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="62"/>
-      <c r="D14" s="158"/>
-      <c r="E14" s="158"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
@@ -32538,8 +32538,8 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="62"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="156"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
@@ -32563,8 +32563,8 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="62"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="158"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
@@ -32588,8 +32588,8 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="62"/>
-      <c r="D17" s="158"/>
-      <c r="E17" s="158"/>
+      <c r="D17" s="156"/>
+      <c r="E17" s="156"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
@@ -32613,8 +32613,8 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="62"/>
-      <c r="D18" s="158"/>
-      <c r="E18" s="158"/>
+      <c r="D18" s="156"/>
+      <c r="E18" s="156"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
@@ -32638,8 +32638,8 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="62"/>
-      <c r="D19" s="158"/>
-      <c r="E19" s="158"/>
+      <c r="D19" s="156"/>
+      <c r="E19" s="156"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
@@ -32663,8 +32663,8 @@
     </row>
     <row r="20" spans="1:26">
       <c r="A20" s="62"/>
-      <c r="D20" s="158"/>
-      <c r="E20" s="158"/>
+      <c r="D20" s="156"/>
+      <c r="E20" s="156"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
@@ -32688,8 +32688,8 @@
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="62"/>
-      <c r="D21" s="158"/>
-      <c r="E21" s="158"/>
+      <c r="D21" s="156"/>
+      <c r="E21" s="156"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
@@ -32713,8 +32713,8 @@
     </row>
     <row r="22" spans="1:26">
       <c r="A22" s="62"/>
-      <c r="D22" s="158"/>
-      <c r="E22" s="158"/>
+      <c r="D22" s="156"/>
+      <c r="E22" s="156"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
@@ -32738,8 +32738,8 @@
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="62"/>
-      <c r="D23" s="158"/>
-      <c r="E23" s="158"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
@@ -32764,8 +32764,8 @@
     <row r="24" spans="1:26">
       <c r="A24" s="62"/>
       <c r="B24" s="62"/>
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
+      <c r="D24" s="156"/>
+      <c r="E24" s="156"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
@@ -32789,8 +32789,8 @@
     </row>
     <row r="25" spans="1:26">
       <c r="A25" s="62"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
+      <c r="D25" s="156"/>
+      <c r="E25" s="156"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -32816,8 +32816,8 @@
       <c r="A26" s="62"/>
       <c r="B26" s="59"/>
       <c r="C26" s="59"/>
-      <c r="D26" s="158"/>
-      <c r="E26" s="158"/>
+      <c r="D26" s="156"/>
+      <c r="E26" s="156"/>
       <c r="F26" s="59"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -32844,8 +32844,8 @@
       <c r="A27" s="62"/>
       <c r="B27" s="59"/>
       <c r="C27" s="59"/>
-      <c r="D27" s="158"/>
-      <c r="E27" s="158"/>
+      <c r="D27" s="156"/>
+      <c r="E27" s="156"/>
       <c r="F27" s="59"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -32870,8 +32870,8 @@
     </row>
     <row r="28" spans="1:26">
       <c r="A28" s="62"/>
-      <c r="D28" s="158"/>
-      <c r="E28" s="158"/>
+      <c r="D28" s="156"/>
+      <c r="E28" s="156"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
@@ -32895,8 +32895,8 @@
     </row>
     <row r="29" spans="1:26">
       <c r="A29" s="62"/>
-      <c r="D29" s="158"/>
-      <c r="E29" s="158"/>
+      <c r="D29" s="156"/>
+      <c r="E29" s="156"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
@@ -32920,8 +32920,8 @@
     </row>
     <row r="30" spans="1:26">
       <c r="A30" s="62"/>
-      <c r="D30" s="158"/>
-      <c r="E30" s="158"/>
+      <c r="D30" s="156"/>
+      <c r="E30" s="156"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
@@ -32945,8 +32945,8 @@
     </row>
     <row r="31" spans="1:26">
       <c r="A31" s="62"/>
-      <c r="D31" s="158"/>
-      <c r="E31" s="158"/>
+      <c r="D31" s="156"/>
+      <c r="E31" s="156"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
@@ -32970,8 +32970,8 @@
     </row>
     <row r="32" spans="1:26">
       <c r="A32" s="62"/>
-      <c r="D32" s="158"/>
-      <c r="E32" s="158"/>
+      <c r="D32" s="156"/>
+      <c r="E32" s="156"/>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
@@ -32995,8 +32995,8 @@
     </row>
     <row r="33" spans="1:26">
       <c r="A33" s="62"/>
-      <c r="D33" s="158"/>
-      <c r="E33" s="158"/>
+      <c r="D33" s="156"/>
+      <c r="E33" s="156"/>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
@@ -33020,8 +33020,8 @@
     </row>
     <row r="34" spans="1:26">
       <c r="A34" s="62"/>
-      <c r="D34" s="158"/>
-      <c r="E34" s="158"/>
+      <c r="D34" s="156"/>
+      <c r="E34" s="156"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
@@ -33045,8 +33045,8 @@
     </row>
     <row r="35" spans="1:26">
       <c r="A35" s="62"/>
-      <c r="D35" s="158"/>
-      <c r="E35" s="158"/>
+      <c r="D35" s="156"/>
+      <c r="E35" s="156"/>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
@@ -33070,8 +33070,8 @@
     </row>
     <row r="36" spans="1:26">
       <c r="A36" s="62"/>
-      <c r="D36" s="158"/>
-      <c r="E36" s="158"/>
+      <c r="D36" s="156"/>
+      <c r="E36" s="156"/>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
@@ -33095,8 +33095,8 @@
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="62"/>
-      <c r="D37" s="158"/>
-      <c r="E37" s="158"/>
+      <c r="D37" s="156"/>
+      <c r="E37" s="156"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
@@ -33120,8 +33120,8 @@
     </row>
     <row r="38" spans="1:26">
       <c r="A38" s="62"/>
-      <c r="D38" s="158"/>
-      <c r="E38" s="158"/>
+      <c r="D38" s="156"/>
+      <c r="E38" s="156"/>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
@@ -33145,8 +33145,8 @@
     </row>
     <row r="39" spans="1:26">
       <c r="A39" s="62"/>
-      <c r="D39" s="158"/>
-      <c r="E39" s="158"/>
+      <c r="D39" s="156"/>
+      <c r="E39" s="156"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
@@ -33170,8 +33170,8 @@
     </row>
     <row r="40" spans="1:26">
       <c r="A40" s="62"/>
-      <c r="D40" s="158"/>
-      <c r="E40" s="158"/>
+      <c r="D40" s="156"/>
+      <c r="E40" s="156"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
@@ -33195,8 +33195,8 @@
     </row>
     <row r="41" spans="1:26">
       <c r="A41" s="62"/>
-      <c r="D41" s="158"/>
-      <c r="E41" s="158"/>
+      <c r="D41" s="156"/>
+      <c r="E41" s="156"/>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
@@ -33220,8 +33220,8 @@
     </row>
     <row r="42" spans="1:26">
       <c r="A42" s="62"/>
-      <c r="D42" s="158"/>
-      <c r="E42" s="158"/>
+      <c r="D42" s="156"/>
+      <c r="E42" s="156"/>
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
@@ -33245,8 +33245,8 @@
     </row>
     <row r="43" spans="1:26">
       <c r="A43" s="62"/>
-      <c r="D43" s="158"/>
-      <c r="E43" s="158"/>
+      <c r="D43" s="156"/>
+      <c r="E43" s="156"/>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -33270,8 +33270,8 @@
     </row>
     <row r="44" spans="1:26">
       <c r="A44" s="62"/>
-      <c r="D44" s="158"/>
-      <c r="E44" s="158"/>
+      <c r="D44" s="156"/>
+      <c r="E44" s="156"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -33295,8 +33295,8 @@
     </row>
     <row r="45" spans="1:26">
       <c r="A45" s="62"/>
-      <c r="D45" s="158"/>
-      <c r="E45" s="158"/>
+      <c r="D45" s="156"/>
+      <c r="E45" s="156"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
@@ -33320,8 +33320,8 @@
     </row>
     <row r="46" spans="1:26">
       <c r="A46" s="62"/>
-      <c r="D46" s="158"/>
-      <c r="E46" s="158"/>
+      <c r="D46" s="156"/>
+      <c r="E46" s="156"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
@@ -33373,52 +33373,52 @@
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="D42:E42"/>
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="D44:E44"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="D46:E46"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -35161,7 +35161,7 @@
       <c r="C19" s="142"/>
       <c r="D19" s="62"/>
       <c r="H19" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
@@ -35184,7 +35184,7 @@
       <c r="C20" s="142"/>
       <c r="D20" s="62"/>
       <c r="H20" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
@@ -35764,58 +35764,58 @@
       <c r="E2" s="58" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="159" t="s">
+      <c r="F2" s="161" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159" t="s">
+      <c r="G2" s="161"/>
+      <c r="H2" s="161" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="159"/>
-      <c r="J2" s="160" t="s">
+      <c r="I2" s="161"/>
+      <c r="J2" s="162" t="s">
         <v>124</v>
       </c>
-      <c r="K2" s="160"/>
-      <c r="L2" s="159" t="s">
+      <c r="K2" s="162"/>
+      <c r="L2" s="161" t="s">
         <v>125</v>
       </c>
-      <c r="M2" s="159"/>
-      <c r="N2" s="160" t="s">
+      <c r="M2" s="161"/>
+      <c r="N2" s="162" t="s">
         <v>126</v>
       </c>
-      <c r="O2" s="160"/>
-      <c r="P2" s="162" t="s">
+      <c r="O2" s="162"/>
+      <c r="P2" s="160" t="s">
         <v>127</v>
       </c>
-      <c r="Q2" s="162"/>
-      <c r="R2" s="156" t="s">
+      <c r="Q2" s="160"/>
+      <c r="R2" s="157" t="s">
         <v>128</v>
       </c>
-      <c r="S2" s="156"/>
-      <c r="T2" s="162" t="s">
+      <c r="S2" s="157"/>
+      <c r="T2" s="160" t="s">
         <v>129</v>
       </c>
-      <c r="U2" s="162"/>
-      <c r="V2" s="156" t="s">
+      <c r="U2" s="160"/>
+      <c r="V2" s="157" t="s">
         <v>130</v>
       </c>
-      <c r="W2" s="156"/>
-      <c r="X2" s="162" t="s">
+      <c r="W2" s="157"/>
+      <c r="X2" s="160" t="s">
         <v>131</v>
       </c>
-      <c r="Y2" s="162"/>
-      <c r="Z2" s="161" t="s">
+      <c r="Y2" s="160"/>
+      <c r="Z2" s="159" t="s">
         <v>132</v>
       </c>
-      <c r="AA2" s="161"/>
-      <c r="AB2" s="161" t="s">
+      <c r="AA2" s="159"/>
+      <c r="AB2" s="159" t="s">
         <v>133</v>
       </c>
-      <c r="AC2" s="161"/>
-      <c r="AD2" s="162" t="s">
+      <c r="AC2" s="159"/>
+      <c r="AD2" s="160" t="s">
         <v>134</v>
       </c>
-      <c r="AE2" s="162"/>
+      <c r="AE2" s="160"/>
       <c r="AF2" s="58" t="s">
         <v>95</v>
       </c>
@@ -37186,6 +37186,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
     <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="AB2:AC2"/>
     <mergeCell ref="AD2:AE2"/>
@@ -37194,11 +37199,6 @@
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{00000000-0002-0000-0700-000000000000}">

--- a/Data/IceStation1c/09aug2025coring/20250809-PS149_32-1-SI_corer_9cm-019-FYI-RHO.xlsx
+++ b/Data/IceStation1c/09aug2025coring/20250809-PS149_32-1-SI_corer_9cm-019-FYI-RHO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evsalg001\Documents\MATLAB\Contrasts coring\Data\IceStation1c\09aug2025coring\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evsalg001\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB0C285-6422-4F47-9A78-40CF3587F1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D5247A-6CC1-4688-A40B-B92789D6C214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="615" windowWidth="19410" windowHeight="20985" tabRatio="726" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="726" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata-core" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="CT" sheetId="12" r:id="rId12"/>
     <sheet name="lists" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="350">
   <si>
     <t>Core</t>
   </si>
@@ -1097,20 +1097,19 @@
     <t>smaller bubbles</t>
   </si>
   <si>
-    <t>Tlab=-22</t>
+    <t>rho_parafine=0.834</t>
   </si>
   <si>
-    <t>rho_parafine=0.834</t>
+    <t>Tlab=-22</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="dd\-mmm\-yy"/>
-    <numFmt numFmtId="166" formatCode="hh:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="165" formatCode="hh:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -1454,8 +1453,8 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1507,11 +1506,11 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="15" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="15" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1957,6 +1956,48 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.5000000000000011E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.22500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.27500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.32499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.42500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.47499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.53499999999999992</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.59499999999999997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.64500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.69500000000000006</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1966,6 +2007,48 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.2999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.6</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2328,46 +2411,46 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>0.8477638067061144</c:v>
+                  <c:v>0.84674852071005913</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.83499999999999996</c:v>
+                  <c:v>0.83399999999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.83499999999999996</c:v>
+                  <c:v>0.83399999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.83499999999999996</c:v>
+                  <c:v>0.83399999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.86841630063445574</c:v>
+                  <c:v>0.86737628111273779</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.87629973968017849</c:v>
+                  <c:v>0.87525027891409446</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.84617659758203789</c:v>
+                  <c:v>0.84516321243523307</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.88781616764147642</c:v>
+                  <c:v>0.88675291474609741</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.85086538868435535</c:v>
+                  <c:v>0.84984638821886505</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.90054374488961564</c:v>
+                  <c:v>0.89946524938675376</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.90533579965850886</c:v>
+                  <c:v>0.90425156516789973</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8785496546796856</c:v>
+                  <c:v>0.87749749940462007</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.89617692907248636</c:v>
+                  <c:v>0.89510366328916613</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.90944022114720124</c:v>
+                  <c:v>0.9083510711817554</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -30045,10 +30128,28 @@
       <c r="AMJ4" s="6"/>
     </row>
     <row r="5" spans="1:1024">
-      <c r="A5" s="141"/>
-      <c r="B5" s="141"/>
-      <c r="C5" s="142"/>
-      <c r="E5" s="62"/>
+      <c r="A5" s="141">
+        <v>0</v>
+      </c>
+      <c r="B5" s="141">
+        <v>0.05</v>
+      </c>
+      <c r="C5" s="142">
+        <f>AVERAGE(A5:B5)</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E5" s="62">
+        <v>0.7</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1.4279999999999999</v>
+      </c>
+      <c r="G5" s="6">
+        <v>16.8</v>
+      </c>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -30065,10 +30166,28 @@
       <c r="AB5" s="9"/>
     </row>
     <row r="6" spans="1:1024">
-      <c r="A6" s="141"/>
-      <c r="B6" s="142"/>
-      <c r="C6" s="142"/>
-      <c r="E6" s="62"/>
+      <c r="A6" s="141">
+        <v>0.05</v>
+      </c>
+      <c r="B6" s="141">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="142">
+        <f t="shared" ref="C6:C18" si="0">AVERAGE(A6:B6)</f>
+        <v>7.5000000000000011E-2</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E6" s="62">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1.1859999999999999</v>
+      </c>
+      <c r="G6" s="6">
+        <v>17.100000000000001</v>
+      </c>
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -30085,10 +30204,28 @@
       <c r="AB6" s="9"/>
     </row>
     <row r="7" spans="1:1024">
-      <c r="A7" s="141"/>
-      <c r="B7" s="141"/>
-      <c r="C7" s="142"/>
-      <c r="E7" s="62"/>
+      <c r="A7" s="141">
+        <v>0.1</v>
+      </c>
+      <c r="B7" s="141">
+        <v>0.15</v>
+      </c>
+      <c r="C7" s="142">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E7" s="62">
+        <v>0.9</v>
+      </c>
+      <c r="F7" s="6">
+        <v>1.871</v>
+      </c>
+      <c r="G7" s="6">
+        <v>16.899999999999999</v>
+      </c>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
       <c r="Q7" s="9"/>
@@ -30105,10 +30242,28 @@
       <c r="AB7" s="9"/>
     </row>
     <row r="8" spans="1:1024">
-      <c r="A8" s="141"/>
-      <c r="B8" s="142"/>
-      <c r="C8" s="142"/>
-      <c r="E8" s="62"/>
+      <c r="A8" s="141">
+        <v>0.15</v>
+      </c>
+      <c r="B8" s="141">
+        <v>0.2</v>
+      </c>
+      <c r="C8" s="142">
+        <f t="shared" si="0"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" s="62">
+        <v>0.9</v>
+      </c>
+      <c r="F8" s="6">
+        <v>1.804</v>
+      </c>
+      <c r="G8" s="6">
+        <v>17.600000000000001</v>
+      </c>
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
       <c r="Q8" s="9"/>
@@ -30125,10 +30280,28 @@
       <c r="AB8" s="9"/>
     </row>
     <row r="9" spans="1:1024">
-      <c r="A9" s="141"/>
-      <c r="B9" s="141"/>
-      <c r="C9" s="142"/>
-      <c r="E9" s="62"/>
+      <c r="A9" s="141">
+        <v>0.2</v>
+      </c>
+      <c r="B9" s="141">
+        <v>0.25</v>
+      </c>
+      <c r="C9" s="142">
+        <f t="shared" si="0"/>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E9" s="62">
+        <v>1.2</v>
+      </c>
+      <c r="F9" s="6">
+        <v>2.38</v>
+      </c>
+      <c r="G9" s="6">
+        <v>17.3</v>
+      </c>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
@@ -30145,10 +30318,28 @@
       <c r="AB9" s="9"/>
     </row>
     <row r="10" spans="1:1024">
-      <c r="A10" s="141"/>
-      <c r="B10" s="142"/>
-      <c r="C10" s="142"/>
-      <c r="E10" s="62"/>
+      <c r="A10" s="141">
+        <v>0.25</v>
+      </c>
+      <c r="B10" s="141">
+        <v>0.3</v>
+      </c>
+      <c r="C10" s="142">
+        <f t="shared" si="0"/>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="E10" s="62">
+        <v>1.6</v>
+      </c>
+      <c r="F10" s="6">
+        <v>3.17</v>
+      </c>
+      <c r="G10" s="6">
+        <v>17.100000000000001</v>
+      </c>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
@@ -30165,10 +30356,28 @@
       <c r="AB10" s="9"/>
     </row>
     <row r="11" spans="1:1024">
-      <c r="A11" s="141"/>
-      <c r="B11" s="141"/>
-      <c r="C11" s="142"/>
-      <c r="E11" s="62"/>
+      <c r="A11" s="141">
+        <v>0.3</v>
+      </c>
+      <c r="B11" s="141">
+        <v>0.35</v>
+      </c>
+      <c r="C11" s="142">
+        <f t="shared" si="0"/>
+        <v>0.32499999999999996</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E11" s="62">
+        <v>2</v>
+      </c>
+      <c r="F11" s="6">
+        <v>3.77</v>
+      </c>
+      <c r="G11" s="6">
+        <v>17.7</v>
+      </c>
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
@@ -30185,10 +30394,28 @@
       <c r="AB11" s="9"/>
     </row>
     <row r="12" spans="1:1024">
-      <c r="A12" s="141"/>
-      <c r="B12" s="142"/>
-      <c r="C12" s="142"/>
-      <c r="E12" s="62"/>
+      <c r="A12" s="141">
+        <v>0.35</v>
+      </c>
+      <c r="B12" s="141">
+        <v>0.4</v>
+      </c>
+      <c r="C12" s="142">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E12" s="62">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F12" s="6">
+        <v>4.33</v>
+      </c>
+      <c r="G12" s="6">
+        <v>18</v>
+      </c>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
@@ -30205,10 +30432,28 @@
       <c r="AB12" s="9"/>
     </row>
     <row r="13" spans="1:1024">
-      <c r="A13" s="141"/>
-      <c r="B13" s="141"/>
-      <c r="C13" s="142"/>
-      <c r="E13" s="62"/>
+      <c r="A13" s="141">
+        <v>0.4</v>
+      </c>
+      <c r="B13" s="141">
+        <v>0.45</v>
+      </c>
+      <c r="C13" s="142">
+        <f t="shared" si="0"/>
+        <v>0.42500000000000004</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E13" s="62">
+        <v>2.8</v>
+      </c>
+      <c r="F13" s="6">
+        <v>5.21</v>
+      </c>
+      <c r="G13" s="6">
+        <v>17.7</v>
+      </c>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
@@ -30225,10 +30470,28 @@
       <c r="AB13" s="9"/>
     </row>
     <row r="14" spans="1:1024">
-      <c r="A14" s="141"/>
-      <c r="B14" s="142"/>
-      <c r="C14" s="142"/>
-      <c r="E14" s="62"/>
+      <c r="A14" s="141">
+        <v>0.45</v>
+      </c>
+      <c r="B14" s="141">
+        <v>0.5</v>
+      </c>
+      <c r="C14" s="142">
+        <f t="shared" si="0"/>
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E14" s="62">
+        <v>3</v>
+      </c>
+      <c r="F14" s="6">
+        <v>5.55</v>
+      </c>
+      <c r="G14" s="6">
+        <v>18</v>
+      </c>
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
@@ -30245,10 +30508,28 @@
       <c r="AB14" s="9"/>
     </row>
     <row r="15" spans="1:1024">
-      <c r="A15" s="141"/>
-      <c r="B15" s="141"/>
-      <c r="C15" s="142"/>
-      <c r="E15" s="62"/>
+      <c r="A15" s="141">
+        <v>0.5</v>
+      </c>
+      <c r="B15" s="141">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="C15" s="142">
+        <f t="shared" si="0"/>
+        <v>0.53499999999999992</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E15" s="62">
+        <v>3.3</v>
+      </c>
+      <c r="F15" s="6">
+        <v>6.1</v>
+      </c>
+      <c r="G15" s="6">
+        <v>16.7</v>
+      </c>
       <c r="O15" s="9"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
@@ -30265,10 +30546,28 @@
       <c r="AB15" s="9"/>
     </row>
     <row r="16" spans="1:1024">
-      <c r="A16" s="141"/>
-      <c r="B16" s="142"/>
-      <c r="C16" s="142"/>
-      <c r="E16" s="62"/>
+      <c r="A16" s="141">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="B16" s="141">
+        <v>0.62</v>
+      </c>
+      <c r="C16" s="142">
+        <f t="shared" si="0"/>
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E16" s="62">
+        <v>2.4</v>
+      </c>
+      <c r="F16" s="6">
+        <v>4.51</v>
+      </c>
+      <c r="G16" s="6">
+        <v>17.2</v>
+      </c>
       <c r="O16" s="9"/>
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
@@ -30285,10 +30584,28 @@
       <c r="AB16" s="9"/>
     </row>
     <row r="17" spans="1:28">
-      <c r="A17" s="141"/>
-      <c r="B17" s="141"/>
-      <c r="C17" s="142"/>
-      <c r="E17" s="62"/>
+      <c r="A17" s="141">
+        <v>0.62</v>
+      </c>
+      <c r="B17" s="141">
+        <v>0.67</v>
+      </c>
+      <c r="C17" s="142">
+        <f t="shared" si="0"/>
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E17" s="62">
+        <v>2.9</v>
+      </c>
+      <c r="F17" s="6">
+        <v>5.45</v>
+      </c>
+      <c r="G17" s="6">
+        <v>18.2</v>
+      </c>
       <c r="O17" s="9"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
@@ -30305,10 +30622,28 @@
       <c r="AB17" s="9"/>
     </row>
     <row r="18" spans="1:28">
-      <c r="A18" s="141"/>
-      <c r="B18" s="142"/>
-      <c r="C18" s="142"/>
-      <c r="E18" s="62"/>
+      <c r="A18" s="141">
+        <v>0.67</v>
+      </c>
+      <c r="B18" s="141">
+        <v>0.72</v>
+      </c>
+      <c r="C18" s="142">
+        <f t="shared" si="0"/>
+        <v>0.69500000000000006</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="E18" s="62">
+        <v>2.6</v>
+      </c>
+      <c r="F18" s="6">
+        <v>4.84</v>
+      </c>
+      <c r="G18" s="6">
+        <v>18</v>
+      </c>
       <c r="O18" s="9"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
@@ -34574,8 +34909,8 @@
         <v>3.1</v>
       </c>
       <c r="G4" s="6">
-        <f>0.835*E4/(E4-F4)</f>
-        <v>0.8477638067061144</v>
+        <f>0.834*E4/(E4-F4)</f>
+        <v>0.84674852071005913</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>338</v>
@@ -34616,7 +34951,7 @@
         <v>336</v>
       </c>
       <c r="G5" s="6">
-        <v>0.83499999999999996</v>
+        <v>0.83399999999999996</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>339</v>
@@ -34657,7 +34992,7 @@
         <v>336</v>
       </c>
       <c r="G6" s="6">
-        <v>0.83499999999999996</v>
+        <v>0.83399999999999996</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>340</v>
@@ -34698,7 +35033,7 @@
         <v>336</v>
       </c>
       <c r="G7" s="6">
-        <v>0.83499999999999996</v>
+        <v>0.83399999999999996</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>340</v>
@@ -34739,8 +35074,8 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="G8" s="6">
-        <f t="shared" ref="G8:G17" si="1">0.835*E8/(E8-F8)</f>
-        <v>0.86841630063445574</v>
+        <f t="shared" ref="G8:G17" si="1">0.834*E8/(E8-F8)</f>
+        <v>0.86737628111273779</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>341</v>
@@ -34782,7 +35117,7 @@
       </c>
       <c r="G9" s="6">
         <f t="shared" si="1"/>
-        <v>0.87629973968017849</v>
+        <v>0.87525027891409446</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>342</v>
@@ -34824,7 +35159,7 @@
       </c>
       <c r="G10" s="6">
         <f t="shared" si="1"/>
-        <v>0.84617659758203789</v>
+        <v>0.84516321243523307</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>343</v>
@@ -34866,7 +35201,7 @@
       </c>
       <c r="G11" s="6">
         <f t="shared" si="1"/>
-        <v>0.88781616764147642</v>
+        <v>0.88675291474609741</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>344</v>
@@ -34908,7 +35243,7 @@
       </c>
       <c r="G12" s="6">
         <f t="shared" si="1"/>
-        <v>0.85086538868435535</v>
+        <v>0.84984638821886505</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>345</v>
@@ -34950,7 +35285,7 @@
       </c>
       <c r="G13" s="6">
         <f t="shared" si="1"/>
-        <v>0.90054374488961564</v>
+        <v>0.89946524938675376</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>346</v>
@@ -34992,7 +35327,7 @@
       </c>
       <c r="G14" s="6">
         <f t="shared" si="1"/>
-        <v>0.90533579965850886</v>
+        <v>0.90425156516789973</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>347</v>
@@ -35034,7 +35369,7 @@
       </c>
       <c r="G15" s="6">
         <f t="shared" si="1"/>
-        <v>0.8785496546796856</v>
+        <v>0.87749749940462007</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>347</v>
@@ -35076,7 +35411,7 @@
       </c>
       <c r="G16" s="6">
         <f t="shared" si="1"/>
-        <v>0.89617692907248636</v>
+        <v>0.89510366328916613</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>347</v>
@@ -35118,7 +35453,7 @@
       </c>
       <c r="G17" s="6">
         <f t="shared" si="1"/>
-        <v>0.90944022114720124</v>
+        <v>0.9083510711817554</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
@@ -35161,7 +35496,7 @@
       <c r="C19" s="142"/>
       <c r="D19" s="62"/>
       <c r="H19" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
@@ -35184,7 +35519,7 @@
       <c r="C20" s="142"/>
       <c r="D20" s="62"/>
       <c r="H20" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
